--- a/JS/liste_etudiants_rectifier.xlsx
+++ b/JS/liste_etudiants_rectifier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephano\Documents\TRAVAIL\Photo-univ\JS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C413D9-97E9-4E93-BE1C-63F7FBAC7AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D17DD35-73ED-48E1-929E-135CCCC0019F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
